--- a/artfynd/A 5042-2022 artfynd.xlsx
+++ b/artfynd/A 5042-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 5042-2022 artfynd.xlsx
+++ b/artfynd/A 5042-2022 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>121143086</v>
       </c>
       <c r="B4" t="n">
-        <v>97988</v>
+        <v>97998</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>121142934</v>
       </c>
       <c r="B5" t="n">
-        <v>97025</v>
+        <v>97035</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 5042-2022 artfynd.xlsx
+++ b/artfynd/A 5042-2022 artfynd.xlsx
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121143086</v>
+        <v>121142934</v>
       </c>
       <c r="B4" t="n">
-        <v>97998</v>
+        <v>97035</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486082</v>
+        <v>486296</v>
       </c>
       <c r="R4" t="n">
-        <v>6539851</v>
+        <v>6539854</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121142934</v>
+        <v>121143086</v>
       </c>
       <c r="B5" t="n">
-        <v>97035</v>
+        <v>97998</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,21 +1010,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486296</v>
+        <v>486082</v>
       </c>
       <c r="R5" t="n">
-        <v>6539854</v>
+        <v>6539851</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 5042-2022 artfynd.xlsx
+++ b/artfynd/A 5042-2022 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>121142934</v>
       </c>
       <c r="B4" t="n">
-        <v>97035</v>
+        <v>97048</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>121143086</v>
       </c>
       <c r="B5" t="n">
-        <v>97998</v>
+        <v>98011</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 5042-2022 artfynd.xlsx
+++ b/artfynd/A 5042-2022 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>121142934</v>
       </c>
       <c r="B4" t="n">
-        <v>97048</v>
+        <v>97049</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>121143086</v>
       </c>
       <c r="B5" t="n">
-        <v>98011</v>
+        <v>98012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 5042-2022 artfynd.xlsx
+++ b/artfynd/A 5042-2022 artfynd.xlsx
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121142934</v>
+        <v>121143086</v>
       </c>
       <c r="B4" t="n">
-        <v>97049</v>
+        <v>98015</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486296</v>
+        <v>486082</v>
       </c>
       <c r="R4" t="n">
-        <v>6539854</v>
+        <v>6539851</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121143086</v>
+        <v>121142934</v>
       </c>
       <c r="B5" t="n">
-        <v>98012</v>
+        <v>97052</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,21 +1010,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486082</v>
+        <v>486296</v>
       </c>
       <c r="R5" t="n">
-        <v>6539851</v>
+        <v>6539854</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 5042-2022 artfynd.xlsx
+++ b/artfynd/A 5042-2022 artfynd.xlsx
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121143086</v>
+        <v>121142934</v>
       </c>
       <c r="B4" t="n">
-        <v>98015</v>
+        <v>97052</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486082</v>
+        <v>486296</v>
       </c>
       <c r="R4" t="n">
-        <v>6539851</v>
+        <v>6539854</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121142934</v>
+        <v>121143086</v>
       </c>
       <c r="B5" t="n">
-        <v>97052</v>
+        <v>98015</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,21 +1010,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486296</v>
+        <v>486082</v>
       </c>
       <c r="R5" t="n">
-        <v>6539854</v>
+        <v>6539851</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 5042-2022 artfynd.xlsx
+++ b/artfynd/A 5042-2022 artfynd.xlsx
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121142934</v>
+        <v>121143086</v>
       </c>
       <c r="B4" t="n">
-        <v>97052</v>
+        <v>98015</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486296</v>
+        <v>486082</v>
       </c>
       <c r="R4" t="n">
-        <v>6539854</v>
+        <v>6539851</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121143086</v>
+        <v>121142934</v>
       </c>
       <c r="B5" t="n">
-        <v>98015</v>
+        <v>97052</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,21 +1010,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486082</v>
+        <v>486296</v>
       </c>
       <c r="R5" t="n">
-        <v>6539851</v>
+        <v>6539854</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 5042-2022 artfynd.xlsx
+++ b/artfynd/A 5042-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>114670113</v>
       </c>
       <c r="B2" t="n">
-        <v>5185</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114670112</v>
+        <v>114670111</v>
       </c>
       <c r="B3" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>208260</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>486062</v>
+        <v>486051</v>
       </c>
       <c r="R3" t="n">
-        <v>6539559</v>
+        <v>6539524</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,12 +877,7 @@
         <v>121143086</v>
       </c>
       <c r="B4" t="n">
-        <v>98015</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,15 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121142934</v>
+        <v>114670112</v>
       </c>
       <c r="B5" t="n">
-        <v>97052</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1028,27 +1008,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hallsberg-Laxå, Nrk</t>
+          <t>Mellan Häggen och Skogstorp, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486296</v>
+        <v>486062</v>
       </c>
       <c r="R5" t="n">
-        <v>6539854</v>
+        <v>6539559</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1072,12 +1044,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-05-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2023-05-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1092,15 +1064,120 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121142934</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hallsberg-Laxå, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>486296</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6539854</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-10-12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-10-12</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Per Karlsson Linderum</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Per Karlsson Linderum</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5042-2022 artfynd.xlsx
+++ b/artfynd/A 5042-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114670113</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114670111</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121143086</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1073,6 +1093,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114670112</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1178,8 +1203,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121142934</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>